--- a/光伏配储项目/电价数据/2026/玳田站.xlsx
+++ b/光伏配储项目/电价数据/2026/玳田站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.75574</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5919500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.10025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42808</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44738</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12555</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13809</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14376</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07762999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11698</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20158</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.8444400000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.32529</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14829</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21985</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23535</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21918</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.7474400000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44086</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15169</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.63719</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.72907</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.9706900000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310599999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.67867</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43133</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6581399999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.31537</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9232</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.6521</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.49978</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.73243</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.89139</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.13473</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.19098</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.66044</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.26307</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86988</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79635</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7569400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51793</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4253</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70809</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.7659</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87022</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91459</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.86741</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.71093</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.80624</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43594</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50871</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.78039</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99472</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52567</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89534</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85056</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7270399999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.40118</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.08793</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03345</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47268</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5468500000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49988</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5248200000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.90659</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6249400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.89546</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.16504</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.43112</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18084</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04141</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.47731</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.37947</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.53488</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.3139</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.36443</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.9207799999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.25687</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.3193</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.36283</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.24894</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.04367</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78862</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80852</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33459</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47184</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.45521</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.57868</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.72962</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.66274</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24283</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55865</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.50132</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8259099999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59635</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7274700000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8155</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.53107</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54012</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80108</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.13281</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.67763</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6012000000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.7234299999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5162899999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50546</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5704400000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54471</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5647000000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26423</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6161</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.20099</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.5056499999999999</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52627</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56635</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.87295</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.90808</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.4195</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.70808</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.73477</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.5992000000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7944</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.83212</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5627000000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.14886</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8044199999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5605399999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48376</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.50018</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34194</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49314</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44517</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42254</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.49564</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.65439</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.55059</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.72838</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.96623</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.6745099999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.74271</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.11706</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.58485</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.22806</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.06858</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.97954</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.20676</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.8045099999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48085</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7540800000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.76249</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.6821900000000001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.17827</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.17757</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49438</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46147</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.89912</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.78713</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.19254</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.76009</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.69552</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.65439</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.57459</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.48779</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31749</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.66212</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.7563799999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.42896</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20293</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.46114</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22475</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15738</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18952</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.53685</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.50756</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22453</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.45782</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21306</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06389</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.11073</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00321</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.06962</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27207</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48491</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34364</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.58362</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04475</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21793</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20927</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07335</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07207</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07031999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33116</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31256</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78522</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88095</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.39617</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.8581599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49316</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5569700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58366</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70616</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87626</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55023</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43289</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.81299</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.56616</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8527</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.62415</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6302000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59299</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.32652</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91352</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44274</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19092</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27424</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.26654</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53042</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8650599999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44337</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1376</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68569</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77595</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63737</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48944</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.42985</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42549</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5230399999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24825</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15553</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00908</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25279</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78346</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30663</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.3214</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24032</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.24455</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23777</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27319</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22969</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.334</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48926</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.98656</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.7049099999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25283</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23928</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.47132</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.47492</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.52259</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.49486</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.7042999999999999</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.78204</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.73311</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.90507</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.66016</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.9362999999999999</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.11441</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40774</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.6339199999999999</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34816</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45885</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47154</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.81748</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.94114</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.93301</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.44082</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.50681</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.18863</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.94402</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.9282899999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.15776</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.89939</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.34816</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.21731</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.25107</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.85126</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.35921</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.54204</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.60287</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.32879</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29692</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.45681</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.72337</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.58026</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.46525</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.5967</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.26671</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.53495</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.8902899999999999</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.70983</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.6734600000000001</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.18639</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.6807300000000001</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.64797</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.7365</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6644800000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.65896</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.17033</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.78534</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.45928</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7649600000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.7468899999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.02186</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.69435</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.65037</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.60502</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5154500000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50302</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24007</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.96629</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30895</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.6575700000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.95656</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.7601</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.05495</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.31144</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.98541</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49327</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.76349</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.75742</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34271</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.6902</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.18404</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.51876</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.55571</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.57936</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6503300000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.59211</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5769099999999999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.8190599999999999</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.66638</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33351</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.18918</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44348</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.74152</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.50802</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.7585599999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.5914199999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.82884</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.6130399999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.6525599999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51736</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.77697</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.67752</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.11611</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.63988</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.8341900000000001</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.64667</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.8237599999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.16451</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.16071</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.19214</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.94837</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.9062100000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.23112</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.7971900000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03421</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.80704</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.61321</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.78481</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.7930199999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7042999999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.21309</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.14285</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.68498</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34973</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52401</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6115900000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49925</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45374</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57356</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.14225</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.83388</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.18949</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.22611</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.55816</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.30573</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.66406</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.6660700000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.68879</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.06981</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.8234</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.57957</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.6109199999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.60203</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.6814199999999999</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.9304600000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.9424600000000001</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.27456</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.65488</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.65951</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.64843</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.64539</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.17243</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4551</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46828</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61498</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7200599999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8079500000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.57926</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7034199999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.87003</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.9899600000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7233999999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76464</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61737</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6656299999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07069</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.75237</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44508</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44161</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43481</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50143</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45717</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.66069</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.63217</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.62698</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.64828</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.63734</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.9336100000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.6492899999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.7265499999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.6859</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7366</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.73579</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15833</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.65752</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41054</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3291</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45619</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.15938</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.95826</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.26078</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24668</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.24191</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09381999999999999</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27045</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03354</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19743</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25092</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.51738</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32144</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7667999999999999</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.23532</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24586</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.23615</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23061</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.23454</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.23454</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.2413</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16068</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26613</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20766</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02115</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01539</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02922</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03836999999999999</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20123</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23857</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32918</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7222999999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6205499999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25698</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25648</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23417</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26861</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25414</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25897</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6559700000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.82221</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8756799999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.84929</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12296</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25769</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06359000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25725</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.4897</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7916299999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77483</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34039</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99526</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.75802</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8360599999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7826900000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83973</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83792</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84224</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9394600000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.74181</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.77864</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74509</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36212</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.60249</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.63373</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5647000000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49292</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45732</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27471</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46825</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44737</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45515</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46321</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.73012</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.60226</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.46906</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46733</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33658</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.54632</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.75789</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.53944</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5297999999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.56163</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.49471</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.46825</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.48729</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.50126</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.18578</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.69011</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49145</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.10611</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.9641900000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.33648</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.83596</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.20682</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.1627</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7205900000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5657000000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45374</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45196</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.7017100000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.85619</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.01905</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.5155700000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23409</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35141</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.15196</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.63486</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.67996</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5551699999999999</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.48305</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.9025700000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7055</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.76902</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.25505</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47501</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.39711</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.02708</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.24616</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.13886</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.06187</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.80104</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.76646</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.74137</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35581</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.22379</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.46562</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.73487</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.1844</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.58013</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.99237</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.19937</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.61593</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.74502</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.30003</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.5844</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.55391</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.36913</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.67425</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.20017</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.58023</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.18754</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.41152</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.20335</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.60082</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.4705299999999999</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.43121</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.47882</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.16195</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.9934500000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.64673</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.29153</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.5634</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.71846</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.69138</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16192</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46528</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.72415</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.79694</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.67264</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.71194</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.67589</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.07686</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.53262</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36234</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.23728</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.95097</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.97405</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.72049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.06019</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.29963</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.18999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.32257</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.25145</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.97754</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.00553</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.58847</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.49911</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.9304199999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14511</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12219</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.61421</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.59589</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.82477</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.58033</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.54366</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.67103</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.8736</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.82569</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.8357</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.8161900000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.71469</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.66062</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7973600000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.94637</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.84074</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.8392500000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.94865</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.8165</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.85427</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.86587</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.8614700000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.93492</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.9459299999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.9540700000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.89824</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.49136</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.20913</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>1.02696</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.86078</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.94316</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.42396</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38366</v>
       </c>
     </row>
   </sheetData>
